--- a/db_master_grants_fullset.xlsx
+++ b/db_master_grants_fullset.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amsterdamumc-my.sharepoint.com/personal/a_p_m_dewi_amsterdamumc_nl/Documents/Funder study R/funders/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amsterdamumc-my.sharepoint.com/personal/a_p_m_dewi_amsterdamumc_nl/Documents/Funder study R/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="8_{A6398F6F-CEB0-407D-B437-51115AF5D1D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4A48A18-C7FC-4164-9F42-E6E44E8DA133}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{EA1B5B57-5197-43BB-8C6C-664C5DA66953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24C39EA7-7EBE-46EB-9AC7-AA6B90F6952F}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2438,7 +2438,7 @@
         <v>70</v>
       </c>
       <c r="J13" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K13" t="s">
         <v>15</v>
